--- a/artfynd/A 59537-2023 artfynd.xlsx
+++ b/artfynd/A 59537-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59537-2023 artfynd.xlsx
+++ b/artfynd/A 59537-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1579,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88574912</v>
+        <v>88575251</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
+        <v>95511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,25 +1591,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221944</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488507.950752767</v>
+        <v>488565.8362613903</v>
       </c>
       <c r="R10" t="n">
-        <v>7003827.796634332</v>
+        <v>7003946.879178762</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88575099</v>
+        <v>88574912</v>
       </c>
       <c r="B11" t="n">
-        <v>95519</v>
+        <v>89392</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488496.1447293738</v>
+        <v>488507.950752767</v>
       </c>
       <c r="R11" t="n">
-        <v>7003816.090335243</v>
+        <v>7003827.796634332</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88575385</v>
+        <v>88575099</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
+        <v>95519</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,25 +1815,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488503.073161342</v>
+        <v>488496.1447293738</v>
       </c>
       <c r="R12" t="n">
-        <v>7003855.828903234</v>
+        <v>7003816.090335243</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1912,6 +1912,118 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>88575385</v>
+      </c>
+      <c r="B13" t="n">
+        <v>89410</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartstugubodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>488503.073161342</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7003855.828903234</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-10-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
